--- a/GameConfig/Datas/通用/功能参数配置表.xlsx
+++ b/GameConfig/Datas/通用/功能参数配置表.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Assets\Projects\DGame\DGame\GameConfig\Datas\通用\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="功能参数配置表" sheetId="1" r:id="rId1"/>
@@ -1360,7 +1365,7 @@
         <v>14</v>
       </c>
       <c r="C11" s="4">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>28</v>
